--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44532,6 +44532,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1921">
+      <c r="A1921" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1921" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1921" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1921" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1921" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1921" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1921" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44555,6 +44555,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1922">
+      <c r="A1922" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1922" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1922" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1922" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1922" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1922" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44578,6 +44578,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1923">
+      <c r="A1923" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1923" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1923" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1923" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1923" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1923" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44601,6 +44601,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1924">
+      <c r="A1924" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1924" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1924" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1924" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1924" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1924" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44465,7 +44465,7 @@
     </row>
     <row r="1918">
       <c r="A1918" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1918" t="n">
         <v>0</v>
@@ -44488,7 +44488,7 @@
     </row>
     <row r="1919">
       <c r="A1919" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1919" t="n">
         <v>0</v>
@@ -44511,7 +44511,7 @@
     </row>
     <row r="1920">
       <c r="A1920" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1920" t="n">
         <v>0</v>
@@ -44534,7 +44534,7 @@
     </row>
     <row r="1921">
       <c r="A1921" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1921" t="n">
         <v>0</v>
@@ -44557,7 +44557,7 @@
     </row>
     <row r="1922">
       <c r="A1922" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1922" t="n">
         <v>0</v>
@@ -44580,7 +44580,7 @@
     </row>
     <row r="1923">
       <c r="A1923" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1923" t="n">
         <v>0</v>
@@ -44603,7 +44603,7 @@
     </row>
     <row r="1924">
       <c r="A1924" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1924" t="n">
         <v>0</v>
@@ -44621,6 +44621,29 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1924" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1925" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1925" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1925" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1925" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44647,6 +44647,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1926">
+      <c r="A1926" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1926" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1926" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1926" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1926" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1927" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1927" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44693,6 +44693,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1928">
+      <c r="A1928" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1928" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1928" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1928" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44716,6 +44716,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1929">
+      <c r="A1929" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1929" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1929" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1929" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44739,6 +44739,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1930">
+      <c r="A1930" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1930" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1930" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1930" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1930" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44762,6 +44762,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1931">
+      <c r="A1931" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1931" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1931" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1931" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44785,6 +44785,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1932">
+      <c r="A1932" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1932" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1932" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1932" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44808,6 +44808,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1933">
+      <c r="A1933" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1933" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1933" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1933" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1933" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1933" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1933" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44831,6 +44831,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1934">
+      <c r="A1934" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1934" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1934" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1934" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44854,6 +44854,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1935">
+      <c r="A1935" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1935" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1935" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1935" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44877,6 +44877,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1936">
+      <c r="A1936" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1936" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1936" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1936" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44900,6 +44900,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1937">
+      <c r="A1937" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1937" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1937" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44923,6 +44923,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1938">
+      <c r="A1938" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1938" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1938" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1938" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1938" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1938" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44946,6 +44946,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1939">
+      <c r="A1939" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1939" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1939" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1939" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1939" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1939" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1939" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44969,6 +44969,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1940">
+      <c r="A1940" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1940" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1940" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1940" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1940" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1940" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1940" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -44992,6 +44992,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1941">
+      <c r="A1941" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1941" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1941" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1941" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1941" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1941" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1941" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -45038,6 +45038,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1943">
+      <c r="A1943" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1943" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1943" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1943" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1943" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1943" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -45061,6 +45061,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1944">
+      <c r="A1944" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1944" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1944" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1944" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1944" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1944" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -45084,6 +45084,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1945">
+      <c r="A1945" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1945" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1945" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1945" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1945" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1945" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -45107,6 +45107,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1946">
+      <c r="A1946" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1946" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1946" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1946" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1946" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1946" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -56841,6 +56841,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1948">
+      <c r="A1948" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1948" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1948" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1948" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1948" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1948" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1948" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1948" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -56870,6 +56870,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1949">
+      <c r="A1949" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1949" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1949" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1949" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1949" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1949" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1949" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1949" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -56899,6 +56899,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1950">
+      <c r="A1950" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1950" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1950" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1950" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1950" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1950" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1950" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1950" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -56928,6 +56928,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1951">
+      <c r="A1951" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1951" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1951" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1951" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1951" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1951" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1951" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1951" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -56957,6 +56957,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1952">
+      <c r="A1952" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1952" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1952" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1952" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1952" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1952" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1952" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1952" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1952" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -56986,6 +56986,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1953">
+      <c r="A1953" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1953" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1953" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1953" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1953" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1953" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1953" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1953" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1953" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -57015,6 +57015,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1954">
+      <c r="A1954" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1954" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1954" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1954" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1954" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1954" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1954" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1954" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1954" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -57044,6 +57044,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1955">
+      <c r="A1955" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1955" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1955" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1955" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1955" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1955" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1955" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1955" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1955" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NSP.MI.xlsx
+++ b/data/NSP.MI.xlsx
@@ -57073,6 +57073,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1956">
+      <c r="A1956" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1956" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1956" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1956" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1956" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F1956" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1956" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1956" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1956" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
